--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\poronga\fuentes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C0850C-CD09-4CAD-8905-E20DADA82BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E262CB-17A4-4CAF-832B-85EFB8392C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="6" xr2:uid="{035B7F24-B472-4BC3-8599-918AE058A668}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="9" xr2:uid="{035B7F24-B472-4BC3-8599-918AE058A668}"/>
   </bookViews>
   <sheets>
     <sheet name="madre" sheetId="2" r:id="rId1"/>
@@ -21,9 +21,10 @@
     <sheet name="Mayo" sheetId="7" r:id="rId6"/>
     <sheet name="Junio" sheetId="8" r:id="rId7"/>
     <sheet name="Julio" sheetId="10" r:id="rId8"/>
+    <sheet name="Agosto" sheetId="12" r:id="rId9"/>
+    <sheet name="Setiembre" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,8 +33,56 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Usuario</author>
+  </authors>
+  <commentList>
+    <comment ref="D95" authorId="0" shapeId="0" xr:uid="{DC559C58-FAC8-4E3F-A7F5-5D5642D33A34}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Decia 299 (error de tipeo). Precio real 39, confirmado por Gonzalo el 09/09/2026.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Usuario</author>
+  </authors>
+  <commentList>
+    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{70176739-1A91-4258-B3DD-7EA538499615}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Sin precio en el WhatsApp del 08/09 (Furlani 1/2, 11 pallets). Completar: hasta que no tenga precio, el script no cuenta este medio camion.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="131">
   <si>
     <t>Productor</t>
   </si>
@@ -305,9 +354,6 @@
     <t>Semana 21</t>
   </si>
   <si>
-    <t>18/05 al 18/23</t>
-  </si>
-  <si>
     <t>Semana 22</t>
   </si>
   <si>
@@ -338,46 +384,97 @@
     <t>22/06 al 27/06</t>
   </si>
   <si>
-    <t>Zapellini</t>
-  </si>
-  <si>
     <t>shapo</t>
   </si>
   <si>
-    <t>zapelini</t>
-  </si>
-  <si>
     <t>josemar</t>
   </si>
   <si>
-    <t>Semana 25</t>
+    <t>Semana 28</t>
   </si>
   <si>
     <t>06/07 al 11/07</t>
   </si>
   <si>
-    <t>Semana 26</t>
+    <t>Semana 29</t>
+  </si>
+  <si>
+    <t>13/07 al 18/07</t>
+  </si>
+  <si>
+    <t>Semana 30</t>
+  </si>
+  <si>
+    <t>20/07 al 25/07</t>
+  </si>
+  <si>
+    <t>Zapelini</t>
+  </si>
+  <si>
+    <t>Semana 31</t>
+  </si>
+  <si>
+    <t>27/07 al 01/08</t>
+  </si>
+  <si>
+    <t>Semana 32</t>
+  </si>
+  <si>
+    <t>03/08 al 08/08</t>
+  </si>
+  <si>
+    <t>Semana 33</t>
+  </si>
+  <si>
+    <t>10/08 al 15/08</t>
+  </si>
+  <si>
+    <t>Semana 34</t>
+  </si>
+  <si>
+    <t>17/08 al 22/08</t>
+  </si>
+  <si>
+    <t>Semana 35</t>
+  </si>
+  <si>
+    <t>24/08 al 29/08</t>
+  </si>
+  <si>
+    <t>Josemar</t>
   </si>
   <si>
     <t>Semana 27</t>
   </si>
   <si>
-    <t>Semana 28</t>
-  </si>
-  <si>
-    <t>13/07 al 18/07</t>
-  </si>
-  <si>
-    <t>20/07 al 25/07</t>
-  </si>
-  <si>
-    <t>27/07 al 1/08</t>
-  </si>
-  <si>
-    <t>Semana 29</t>
-  </si>
-  <si>
     <t>29/06 al 04/07</t>
+  </si>
+  <si>
+    <t>Semana 36</t>
+  </si>
+  <si>
+    <t>31/08 al 05/09</t>
+  </si>
+  <si>
+    <t>Maicol</t>
+  </si>
+  <si>
+    <t>Shapo</t>
+  </si>
+  <si>
+    <t>media carga exóticos</t>
+  </si>
+  <si>
+    <t>18/05 al 23/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana </t>
+  </si>
+  <si>
+    <t>Semana 37</t>
+  </si>
+  <si>
+    <t>07/09 al 12/09</t>
   </si>
 </sst>
 </file>
@@ -387,7 +484,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,8 +552,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,6 +582,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,7 +726,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -691,6 +801,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1026,18 +1137,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
@@ -1246,18 +1357,18 @@
       <c r="F26" s="1"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
     </row>
     <row r="33" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
@@ -1464,18 +1575,18 @@
       <c r="F54" s="1"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C58" s="42" t="s">
+      <c r="C58" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C59" s="42" t="s">
+      <c r="C59" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
     </row>
     <row r="61" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
@@ -1682,18 +1793,18 @@
       <c r="F82" s="1"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C86" s="42" t="s">
+      <c r="C86" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D86" s="42"/>
-      <c r="E86" s="42"/>
+      <c r="D86" s="43"/>
+      <c r="E86" s="43"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C87" s="42" t="s">
+      <c r="C87" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D87" s="42"/>
-      <c r="E87" s="42"/>
+      <c r="D87" s="43"/>
+      <c r="E87" s="43"/>
     </row>
     <row r="89" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
@@ -1914,6 +2025,894 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
+  <dimension ref="B2:J105"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="11" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+    </row>
+    <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="11">
+        <f>SUM(C21,C36,C54,C73,C91)</f>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>35</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="11" t="e">
+        <f>AVERAGE(D21,D36,D54,D73,D91)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>35</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>35</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
+        <v>35</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>35</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>35</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>35</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>38</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>38</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>38</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>38</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7">
+        <v>38</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <v>38</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>38</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="17">
+        <f>SUM(C6:C20)</f>
+        <v>14.5</v>
+      </c>
+      <c r="D21" s="18">
+        <f>AVERAGE(D6:D20)</f>
+        <v>36.5</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
+    </row>
+    <row r="22" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C25" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+    </row>
+    <row r="26" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+    </row>
+    <row r="28" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+    </row>
+    <row r="31" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+    </row>
+    <row r="32" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="34" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+    </row>
+    <row r="35" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+    </row>
+    <row r="36" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="17">
+        <f>SUM(C29:C35)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="18" t="e">
+        <f>AVERAGE(D29:D35)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E36" s="32"/>
+      <c r="F36" s="33"/>
+    </row>
+    <row r="37" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+    </row>
+    <row r="41" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="44"/>
+    </row>
+    <row r="42" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+    </row>
+    <row r="51" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+    </row>
+    <row r="52" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+    </row>
+    <row r="53" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+    </row>
+    <row r="54" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="17">
+        <f>SUM(C44:C53)</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="18" t="e">
+        <f>AVERAGE(D44:D53)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E54" s="32"/>
+      <c r="F54" s="33"/>
+    </row>
+    <row r="55" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+    </row>
+    <row r="59" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+    </row>
+    <row r="60" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+    </row>
+    <row r="63" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+    </row>
+    <row r="72" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72" s="5"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
+    </row>
+    <row r="73" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="17">
+        <f>SUM(C62:C72)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="18" t="e">
+        <f>AVERAGE(D62:D72)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E73" s="32"/>
+      <c r="F73" s="33"/>
+    </row>
+    <row r="74" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+    </row>
+    <row r="78" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="44"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="44"/>
+    </row>
+    <row r="79" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="5"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+    </row>
+    <row r="82" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="5"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+    </row>
+    <row r="83" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="5"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
+    </row>
+    <row r="84" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="5"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="10"/>
+      <c r="F84" s="10"/>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="5"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="5"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B87" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C87" s="5"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C88" s="5"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B89" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" s="5"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+    </row>
+    <row r="90" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C90" s="5"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="10"/>
+    </row>
+    <row r="91" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" s="17">
+        <f>SUM(C81:C90)</f>
+        <v>0</v>
+      </c>
+      <c r="D91" s="18" t="e">
+        <f>AVERAGE(D81:D90)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E91" s="32"/>
+      <c r="F91" s="33"/>
+    </row>
+    <row r="93" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21814FA0-A3A7-4DFD-B521-00CFACE52E60}">
   <dimension ref="B2:I105"/>
@@ -1926,18 +2925,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -2127,18 +3126,18 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
     </row>
     <row r="19" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
@@ -2490,18 +3489,18 @@
       </c>
     </row>
     <row r="43" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C43" s="43" t="s">
+      <c r="C43" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
     </row>
     <row r="44" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C44" s="43" t="s">
+      <c r="C44" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
     </row>
     <row r="46" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
@@ -2836,18 +3835,18 @@
       </c>
     </row>
     <row r="69" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C69" s="43" t="s">
+      <c r="C69" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
     </row>
     <row r="70" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C70" s="43" t="s">
+      <c r="C70" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="D70" s="43"/>
-      <c r="E70" s="43"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
     </row>
     <row r="72" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
@@ -3158,18 +4157,18 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C93" s="43" t="s">
+      <c r="C93" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D93" s="43"/>
-      <c r="E93" s="43"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="44"/>
     </row>
     <row r="94" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C94" s="43" t="s">
+      <c r="C94" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="D94" s="43"/>
-      <c r="E94" s="43"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="44"/>
     </row>
     <row r="96" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
@@ -3350,18 +4349,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3643,18 +4642,18 @@
       </c>
     </row>
     <row r="24" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
@@ -3910,18 +4909,18 @@
       </c>
     </row>
     <row r="45" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C45" s="43" t="s">
+      <c r="C45" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
     </row>
     <row r="46" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C46" s="43" t="s">
+      <c r="C46" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
     </row>
     <row r="48" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
@@ -4164,18 +5163,18 @@
       </c>
     </row>
     <row r="65" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C65" s="43" t="s">
+      <c r="C65" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
     </row>
     <row r="66" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C66" s="43" t="s">
+      <c r="C66" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
     </row>
     <row r="68" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B68" s="4" t="s">
@@ -4461,18 +5460,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4627,7 +5626,7 @@
     </row>
     <row r="13" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
@@ -4644,7 +5643,7 @@
     </row>
     <row r="14" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="5">
         <v>1</v>
@@ -4798,18 +5797,18 @@
       </c>
     </row>
     <row r="26" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
@@ -5101,18 +6100,18 @@
       </c>
     </row>
     <row r="49" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
     </row>
     <row r="50" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C50" s="43" t="s">
+      <c r="C50" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
     </row>
     <row r="52" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
@@ -5235,7 +6234,7 @@
     </row>
     <row r="59" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C59" s="5">
         <v>1</v>
@@ -5474,18 +6473,18 @@
       </c>
     </row>
     <row r="76" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C76" s="43" t="s">
+      <c r="C76" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="43"/>
-      <c r="E76" s="43"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="44"/>
     </row>
     <row r="77" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C77" s="43" t="s">
+      <c r="C77" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="43"/>
-      <c r="E77" s="43"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
     </row>
     <row r="79" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
@@ -5862,7 +6861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD19006-C29F-427C-89CA-75DD77CA8367}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD19006-C29F-427C-89CA-75DD77CA8367}">
   <dimension ref="B2:K107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5873,18 +6872,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5932,7 +6931,7 @@
       </c>
       <c r="K6" s="40">
         <f>AVERAGE(D12,D41,D65,D88,D107)</f>
-        <v>40.748571428571424</v>
+        <v>36.415238095238095</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6040,18 +7039,18 @@
       </c>
     </row>
     <row r="16" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
@@ -6447,18 +7446,18 @@
       </c>
     </row>
     <row r="45" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C45" s="43" t="s">
+      <c r="C45" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
     </row>
     <row r="46" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C46" s="43" t="s">
+      <c r="C46" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
     </row>
     <row r="48" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
@@ -6765,18 +7764,18 @@
       <c r="F65" s="33"/>
     </row>
     <row r="69" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C69" s="43" t="s">
+      <c r="C69" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
     </row>
     <row r="70" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C70" s="43" t="s">
+      <c r="C70" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="D70" s="43"/>
-      <c r="E70" s="43"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
     </row>
     <row r="72" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
@@ -7035,7 +8034,7 @@
     </row>
     <row r="87" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C87" s="14">
         <v>1</v>
@@ -7066,18 +8065,18 @@
       <c r="F88" s="33"/>
     </row>
     <row r="91" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C91" s="43" t="s">
+      <c r="C91" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="D91" s="43"/>
-      <c r="E91" s="43"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="44"/>
     </row>
     <row r="92" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C92" s="43" t="s">
+      <c r="C92" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="D92" s="43"/>
-      <c r="E92" s="43"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
     </row>
     <row r="94" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
@@ -7104,7 +8103,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="7">
-        <v>299</v>
+        <v>39</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>79</v>
@@ -7217,7 +8216,7 @@
     </row>
     <row r="102" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C102" s="5">
         <v>1</v>
@@ -7310,7 +8309,7 @@
       </c>
       <c r="D107" s="18">
         <f>AVERAGE(D95:D106)</f>
-        <v>53.75</v>
+        <v>32.083333333333336</v>
       </c>
       <c r="E107" s="32"/>
       <c r="F107" s="33"/>
@@ -7329,6 +8328,7 @@
     <mergeCell ref="C46:E46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7344,18 +8344,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7620,18 +8620,18 @@
       <c r="F19" s="33"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
@@ -7802,18 +8802,18 @@
       <c r="F35" s="33"/>
     </row>
     <row r="39" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C39" s="43" t="s">
+      <c r="C39" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
     </row>
     <row r="40" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C40" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
+      <c r="C40" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
     </row>
     <row r="42" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
@@ -7974,18 +8974,18 @@
       <c r="F51" s="35"/>
     </row>
     <row r="55" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C55" s="43" t="s">
+      <c r="C55" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+    </row>
+    <row r="56" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C56" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-    </row>
-    <row r="56" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C56" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
     </row>
     <row r="58" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
@@ -8108,7 +9108,7 @@
     </row>
     <row r="65" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C65" s="5">
         <v>1</v>
@@ -8298,18 +9298,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="C3" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8430,7 +9430,7 @@
     </row>
     <row r="11" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -8580,18 +9580,18 @@
       <c r="F19" s="33"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C24" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
+      <c r="C24" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
@@ -8712,7 +9712,7 @@
     </row>
     <row r="33" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" s="5">
         <v>0.5</v>
@@ -8841,18 +9841,18 @@
       <c r="F40" s="33"/>
     </row>
     <row r="44" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C44" s="43" t="s">
+      <c r="C44" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+    </row>
+    <row r="45" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C45" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-    </row>
-    <row r="45" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C45" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
     </row>
     <row r="47" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
@@ -8975,7 +9975,7 @@
     </row>
     <row r="54" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C54" s="5">
         <v>1</v>
@@ -9009,7 +10009,7 @@
     </row>
     <row r="56" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
@@ -9026,7 +10026,7 @@
     </row>
     <row r="57" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C57" s="5">
         <v>1</v>
@@ -9108,18 +10108,18 @@
       <c r="F61" s="35"/>
     </row>
     <row r="65" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C65" s="43" t="s">
+      <c r="C65" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+    </row>
+    <row r="66" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C66" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43"/>
-    </row>
-    <row r="66" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C66" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
     </row>
     <row r="68" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B68" s="4" t="s">
@@ -9259,7 +10259,7 @@
     </row>
     <row r="76" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C76" s="5">
         <v>1</v>
@@ -9381,33 +10381,32 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44F2AFCA-6793-4621-B2DC-40D85773A982}">
-  <dimension ref="B2:K99"/>
+  <dimension ref="B2:J98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="4" width="9.7109375" customWidth="1"/>
     <col min="5" max="6" width="13.85546875" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="10" max="11" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-    </row>
-    <row r="3" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-    </row>
-    <row r="4" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+    </row>
+    <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -9423,14 +10422,17 @@
       <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="I5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="11"/>
-    </row>
-    <row r="6" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J5" s="11">
+        <f>SUM(C16,C32,C51,C69,C81)</f>
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -9444,14 +10446,17 @@
       <c r="F6" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="11"/>
-    </row>
-    <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="11">
+        <f>AVERAGE(D16,D32,D51,D69,D81)</f>
+        <v>43.06909090909091</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
@@ -9466,32 +10471,32 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
       </c>
       <c r="D8" s="7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
       </c>
       <c r="D9" s="7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>8</v>
@@ -9500,9 +10505,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
@@ -9511,15 +10516,15 @@
         <v>44</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -9528,13 +10533,13 @@
         <v>44</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>67</v>
       </c>
@@ -9551,9 +10556,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
@@ -9562,47 +10567,47 @@
         <v>44</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="C14" s="5">
         <v>1</v>
       </c>
       <c r="D14" s="7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5">
         <v>1</v>
       </c>
       <c r="D15" s="7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
         <v>20</v>
       </c>
@@ -9617,49 +10622,1061 @@
       <c r="E16" s="32"/>
       <c r="F16" s="33"/>
     </row>
+    <row r="20" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C20" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+    </row>
+    <row r="21" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C21" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+    </row>
+    <row r="22" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7">
+        <v>40</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7">
+        <v>40</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7">
+        <v>44</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7">
+        <v>40</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="5">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7">
+        <v>44</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7">
+        <v>44</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7">
+        <v>44</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7">
+        <v>44</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="17">
+        <f>SUM(C24:C31)</f>
+        <v>8</v>
+      </c>
+      <c r="D32" s="18">
+        <f>AVERAGE(D24:D31)</f>
+        <v>42.5</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="33"/>
+    </row>
+    <row r="33" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+    </row>
+    <row r="37" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C37" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+    </row>
+    <row r="39" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7">
+        <v>40</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7">
+        <v>40</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>40</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7">
+        <v>40</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7">
+        <v>44</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7">
+        <v>44</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="5">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7">
+        <v>44</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7">
+        <v>44</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="5">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7">
+        <v>44</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="5">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7">
+        <v>44</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7">
+        <v>44</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="17">
+        <f>SUM(C40:C50)</f>
+        <v>11</v>
+      </c>
+      <c r="D51" s="18">
+        <f>AVERAGE(D40:D50)</f>
+        <v>42.545454545454547</v>
+      </c>
+      <c r="E51" s="32"/>
+      <c r="F51" s="33"/>
+    </row>
+    <row r="52" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+    </row>
+    <row r="56" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+    </row>
+    <row r="58" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B58" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1</v>
+      </c>
+      <c r="D59" s="7">
+        <v>40</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7">
+        <v>42</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7">
+        <v>42</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7">
+        <v>43</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="5">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7">
+        <v>44</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7">
+        <v>44</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" s="5">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7">
+        <v>44</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" s="5">
+        <v>1</v>
+      </c>
+      <c r="D66" s="7">
+        <v>44</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C67" s="5">
+        <v>1</v>
+      </c>
+      <c r="D67" s="7">
+        <v>44</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D68" s="7">
+        <v>44</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B69" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="17">
+        <f>SUM(C59:C68)</f>
+        <v>9.5</v>
+      </c>
+      <c r="D69" s="18">
+        <f>AVERAGE(D59:D68)</f>
+        <v>43.1</v>
+      </c>
+      <c r="E69" s="32"/>
+      <c r="F69" s="33"/>
+    </row>
+    <row r="70" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C73" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D73" s="44"/>
+      <c r="E73" s="44"/>
+    </row>
+    <row r="74" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" s="44"/>
+      <c r="E74" s="44"/>
+    </row>
+    <row r="75" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="5">
+        <v>1</v>
+      </c>
+      <c r="D77" s="7">
+        <v>44</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="5">
+        <v>1</v>
+      </c>
+      <c r="D78" s="7">
+        <v>45</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="5">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7">
+        <v>44</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="5">
+        <v>1</v>
+      </c>
+      <c r="D80" s="7">
+        <v>47</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="17">
+        <f>SUM(C77:C80)</f>
+        <v>4</v>
+      </c>
+      <c r="D81" s="18">
+        <f>AVERAGE(D77:D80)</f>
+        <v>45</v>
+      </c>
+      <c r="E81" s="32"/>
+      <c r="F81" s="33"/>
+    </row>
+    <row r="86" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C36:E36"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19641899-B459-4174-9EE5-03A0F974A9D7}">
+  <dimension ref="B2:J98"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="11" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+    </row>
+    <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="11">
+        <f>SUM(C14,C29,C47,C66,C84)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>44</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="11">
+        <f>AVERAGE(D14,D29,D47,D66,D84)</f>
+        <v>40.882987012987009</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>47</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>44</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
+        <v>47</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>47</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>47</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>47</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>47</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="17">
+        <f>SUM(C6:C13)</f>
+        <v>8</v>
+      </c>
+      <c r="D14" s="18">
+        <f>AVERAGE(D6:D13)</f>
+        <v>46.25</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
+    </row>
+    <row r="15" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C18" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+    </row>
     <row r="19" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C19" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-    </row>
-    <row r="20" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C20" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
+      <c r="C19" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+    </row>
+    <row r="21" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>17</v>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7">
+        <v>46</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="C23" s="5">
         <v>1</v>
       </c>
       <c r="D23" s="7">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>58</v>
@@ -9667,47 +11684,47 @@
     </row>
     <row r="24" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
       </c>
       <c r="D24" s="7">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
       </c>
       <c r="D25" s="7">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
       </c>
       <c r="D26" s="7">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>8</v>
@@ -9718,215 +11735,219 @@
     </row>
     <row r="27" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C27" s="5">
         <v>1</v>
       </c>
       <c r="D27" s="7">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="C28" s="5">
         <v>1</v>
       </c>
       <c r="D28" s="7">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="5">
-        <v>1</v>
-      </c>
-      <c r="D29" s="7">
-        <v>35</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="5">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7">
-        <v>35</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D31" s="7">
-        <v>35</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D32" s="7">
-        <v>35</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
+    <row r="29" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="17">
+        <f>SUM(C22:C28)</f>
+        <v>7</v>
+      </c>
+      <c r="D29" s="18">
+        <f>AVERAGE(D22:D28)</f>
+        <v>44.428571428571431</v>
+      </c>
+      <c r="E29" s="32"/>
+      <c r="F29" s="33"/>
+    </row>
+    <row r="30" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D33" s="7">
-        <v>35</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>58</v>
-      </c>
+      <c r="C33" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
     </row>
     <row r="34" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+    </row>
+    <row r="35" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7">
+        <v>40</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="5">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7">
+        <v>40</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="7">
+        <v>39</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7">
+        <v>39</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D34" s="7">
-        <v>32</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1</v>
-      </c>
-      <c r="D35" s="7">
-        <v>46</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="17">
-        <f>SUM(C23:C35)</f>
-        <v>11</v>
-      </c>
-      <c r="D36" s="18">
-        <f>AVERAGE(D23:D35)</f>
-        <v>34.769230769230766</v>
-      </c>
-      <c r="E36" s="32"/>
-      <c r="F36" s="33"/>
-    </row>
-    <row r="40" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C40" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-    </row>
-    <row r="41" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C41" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-    </row>
-    <row r="43" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>17</v>
+      <c r="C41" s="5">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7">
+        <v>40</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>40</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7">
+        <v>40</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C44" s="5">
         <v>1</v>
       </c>
       <c r="D44" s="7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>58</v>
@@ -9934,166 +11955,86 @@
     </row>
     <row r="45" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C45" s="5">
         <v>1</v>
       </c>
       <c r="D45" s="7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C46" s="5">
         <v>1</v>
       </c>
       <c r="D46" s="7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1</v>
-      </c>
-      <c r="D47" s="7">
-        <v>36</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="5">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7">
-        <v>36</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D49" s="7">
-        <v>39</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F49" s="10"/>
-    </row>
-    <row r="50" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D50" s="7">
-        <v>39</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F50" s="10"/>
-    </row>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="17">
+        <f>SUM(C37:C46)</f>
+        <v>10</v>
+      </c>
+      <c r="D47" s="18">
+        <f>AVERAGE(D37:D46)</f>
+        <v>39.799999999999997</v>
+      </c>
+      <c r="E47" s="32"/>
+      <c r="F47" s="33"/>
+    </row>
+    <row r="48" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" s="5">
-        <v>1</v>
-      </c>
-      <c r="D51" s="7">
-        <v>39</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F51" s="10"/>
+      <c r="C51" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
     </row>
     <row r="52" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7">
-        <v>39</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C53" s="5">
-        <v>1</v>
-      </c>
-      <c r="D53" s="7">
-        <v>39</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
+      <c r="C52" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+    </row>
+    <row r="53" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1</v>
-      </c>
-      <c r="D54" s="7">
-        <v>39</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>58</v>
+      <c r="B54" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -10107,13 +12048,13 @@
         <v>38</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>9</v>
       </c>
@@ -10124,223 +12065,227 @@
         <v>38</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="13" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="5">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7">
+        <v>36</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1</v>
+      </c>
+      <c r="D58" s="7">
+        <v>36</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1</v>
+      </c>
+      <c r="D59" s="7">
+        <v>38</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7">
+        <v>38</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7">
+        <v>38</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7">
+        <v>38</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="5">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7">
+        <v>38</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7">
+        <v>38</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="5">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7">
+        <v>38</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C57" s="17">
-        <f>SUM(C44:C56)</f>
-        <v>12</v>
-      </c>
-      <c r="D57" s="18">
-        <f>AVERAGE(D44:D56)</f>
-        <v>37.692307692307693</v>
-      </c>
-      <c r="E57" s="32"/>
-      <c r="F57" s="33"/>
-    </row>
-    <row r="61" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C61" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61" s="43"/>
-      <c r="E61" s="43"/>
-    </row>
-    <row r="62" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C62" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="D62" s="43"/>
-      <c r="E62" s="43"/>
-    </row>
-    <row r="64" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
+      <c r="C66" s="17">
+        <f>SUM(C55:C65)</f>
+        <v>11</v>
+      </c>
+      <c r="D66" s="18">
+        <f>AVERAGE(D55:D65)</f>
+        <v>37.636363636363633</v>
+      </c>
+      <c r="E66" s="32"/>
+      <c r="F66" s="33"/>
+    </row>
+    <row r="67" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+    </row>
+    <row r="71" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44"/>
+    </row>
+    <row r="72" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C73" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="4" t="s">
+      <c r="D73" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F73" s="4" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="5">
-        <v>1</v>
-      </c>
-      <c r="D65" s="7">
-        <v>42</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="5">
-        <v>1</v>
-      </c>
-      <c r="D66" s="7">
-        <v>40</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C67" s="5">
-        <v>1</v>
-      </c>
-      <c r="D67" s="7">
-        <v>40</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="5">
-        <v>1</v>
-      </c>
-      <c r="D68" s="7">
-        <v>44</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C69" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D69" s="7">
-        <v>44</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C70" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D70" s="7">
-        <v>44</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C71" s="5">
-        <v>1</v>
-      </c>
-      <c r="D71" s="7">
-        <v>44</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F71" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C72" s="5">
-        <v>1</v>
-      </c>
-      <c r="D72" s="7">
-        <v>44</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="5">
-        <v>1</v>
-      </c>
-      <c r="D73" s="7">
-        <v>44</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
-        <v>104</v>
+        <v>9</v>
       </c>
       <c r="C74" s="5">
         <v>1</v>
       </c>
       <c r="D74" s="7">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>58</v>
@@ -10354,10 +12299,10 @@
         <v>1</v>
       </c>
       <c r="D75" s="7">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>58</v>
@@ -10365,13 +12310,13 @@
     </row>
     <row r="76" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C76" s="5">
         <v>1</v>
       </c>
       <c r="D76" s="7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>8</v>
@@ -10380,15 +12325,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C77" s="5">
         <v>1</v>
       </c>
       <c r="D77" s="7">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>8</v>
@@ -10397,290 +12342,148 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="13" t="s">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="5">
+        <v>1</v>
+      </c>
+      <c r="D78" s="7">
+        <v>35</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="5">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7">
+        <v>35</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C80" s="5">
+        <v>1</v>
+      </c>
+      <c r="D80" s="7">
+        <v>38</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C81" s="5">
+        <v>1</v>
+      </c>
+      <c r="D81" s="7">
+        <v>38</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C82" s="5">
+        <v>1</v>
+      </c>
+      <c r="D82" s="7">
+        <v>38</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="5">
+        <v>1</v>
+      </c>
+      <c r="D83" s="7">
+        <v>37</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C78" s="17">
-        <f>SUM(C65:C77)</f>
-        <v>12</v>
-      </c>
-      <c r="D78" s="18">
-        <f>AVERAGE(D65:D77)</f>
-        <v>42.615384615384613</v>
-      </c>
-      <c r="E78" s="34"/>
-      <c r="F78" s="35"/>
-    </row>
-    <row r="82" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C82" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43"/>
-    </row>
-    <row r="83" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C83" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="D83" s="43"/>
-      <c r="E83" s="43"/>
-    </row>
-    <row r="85" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B85" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C86" s="5">
-        <v>1</v>
-      </c>
-      <c r="D86" s="7">
-        <v>42</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="87" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C87" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D87" s="7">
-        <v>42</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C88" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D88" s="7">
-        <v>44</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="89" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="5">
-        <v>1</v>
-      </c>
-      <c r="D89" s="7">
-        <v>40</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F89" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="5">
-        <v>1</v>
-      </c>
-      <c r="D90" s="7">
-        <v>40</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="91" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C91" s="5">
-        <v>1</v>
-      </c>
-      <c r="D91" s="7">
-        <v>44</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C92" s="5">
-        <v>1</v>
-      </c>
-      <c r="D92" s="7">
-        <v>44</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" s="5">
-        <v>1</v>
-      </c>
-      <c r="D93" s="7">
-        <v>44</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" s="5">
-        <v>1</v>
-      </c>
-      <c r="D94" s="7">
-        <v>40</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="5">
-        <v>1</v>
-      </c>
-      <c r="D95" s="7">
-        <v>40</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C96" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D96" s="7">
-        <v>44</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C97" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D97" s="7">
-        <v>44</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="2:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="1"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16"/>
-    </row>
-    <row r="99" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C99" s="17">
-        <f>SUM(C86:C98)</f>
+      <c r="C84" s="17">
+        <f>SUM(C74:C83)</f>
         <v>10</v>
       </c>
-      <c r="D99" s="18">
-        <f>AVERAGE(D86:D98)</f>
-        <v>42.333333333333336</v>
-      </c>
-      <c r="E99" s="34"/>
-      <c r="F99" s="35"/>
-    </row>
+      <c r="D84" s="18">
+        <f>AVERAGE(D74:D83)</f>
+        <v>36.299999999999997</v>
+      </c>
+      <c r="E84" s="32"/>
+      <c r="F84" s="33"/>
+    </row>
+    <row r="86" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -2406,7 +2406,9 @@
       <c r="C29" s="6">
         <v>1</v>
       </c>
-      <c r="D29" s="8"/>
+      <c r="D29" s="8">
+        <v>38</v>
+      </c>
       <c r="E29" s="11" t="s">
         <v>24</v>
       </c>
@@ -2421,7 +2423,9 @@
       <c r="C30" s="6">
         <v>1</v>
       </c>
-      <c r="D30" s="8"/>
+      <c r="D30" s="8">
+        <v>35</v>
+      </c>
       <c r="E30" s="11" t="s">
         <v>34</v>
       </c>
@@ -2436,7 +2440,9 @@
       <c r="C31" s="6">
         <v>1</v>
       </c>
-      <c r="D31" s="8"/>
+      <c r="D31" s="8">
+        <v>43</v>
+      </c>
       <c r="E31" s="11" t="s">
         <v>29</v>
       </c>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -2043,7 +2043,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="B2:J91"/>
+  <dimension ref="B2:J92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -2088,7 +2088,7 @@
         <v>18</v>
       </c>
       <c r="J5" s="12">
-        <f>SUM(C21,C36,C54,C73,C91)</f>
+        <f>SUM(C21,C36,C54,C74,C92)</f>
         <v>14.5</v>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
         <v>21</v>
       </c>
       <c r="J6" s="12" t="e">
-        <f>AVERAGE(D21,D36,D54,D73,D91)</f>
+        <f>AVERAGE(D21,D36,D54,D74,D92)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2693,7 +2693,9 @@
       <c r="C62" s="6">
         <v>1</v>
       </c>
-      <c r="D62" s="8"/>
+      <c r="D62" s="8">
+        <v>36</v>
+      </c>
       <c r="E62" s="11" t="s">
         <v>29</v>
       </c>
@@ -2708,7 +2710,9 @@
       <c r="C63" s="6">
         <v>1</v>
       </c>
-      <c r="D63" s="8"/>
+      <c r="D63" s="8">
+        <v>36</v>
+      </c>
       <c r="E63" s="11" t="s">
         <v>29</v>
       </c>
@@ -2723,7 +2727,9 @@
       <c r="C64" s="6">
         <v>1</v>
       </c>
-      <c r="D64" s="8"/>
+      <c r="D64" s="8">
+        <v>35</v>
+      </c>
       <c r="E64" s="11" t="s">
         <v>24</v>
       </c>
@@ -2733,12 +2739,14 @@
     </row>
     <row r="65">
       <c r="B65" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6">
         <v>1</v>
       </c>
-      <c r="D65" s="8"/>
+      <c r="D65" s="8">
+        <v>35</v>
+      </c>
       <c r="E65" s="11" t="s">
         <v>24</v>
       </c>
@@ -2753,7 +2761,9 @@
       <c r="C66" s="6">
         <v>1</v>
       </c>
-      <c r="D66" s="8"/>
+      <c r="D66" s="8">
+        <v>43</v>
+      </c>
       <c r="E66" s="11" t="s">
         <v>27</v>
       </c>
@@ -2768,7 +2778,9 @@
       <c r="C67" s="6">
         <v>1</v>
       </c>
-      <c r="D67" s="8"/>
+      <c r="D67" s="8">
+        <v>43</v>
+      </c>
       <c r="E67" s="11" t="s">
         <v>27</v>
       </c>
@@ -2783,7 +2795,9 @@
       <c r="C68" s="6">
         <v>1</v>
       </c>
-      <c r="D68" s="8"/>
+      <c r="D68" s="8">
+        <v>35</v>
+      </c>
       <c r="E68" s="11" t="s">
         <v>34</v>
       </c>
@@ -2798,7 +2812,9 @@
       <c r="C69" s="6">
         <v>1</v>
       </c>
-      <c r="D69" s="8"/>
+      <c r="D69" s="8">
+        <v>40</v>
+      </c>
       <c r="E69" s="11" t="s">
         <v>24</v>
       </c>
@@ -2813,7 +2829,9 @@
       <c r="C70" s="6">
         <v>1</v>
       </c>
-      <c r="D70" s="8"/>
+      <c r="D70" s="8">
+        <v>43</v>
+      </c>
       <c r="E70" s="11" t="s">
         <v>24</v>
       </c>
@@ -2828,7 +2846,9 @@
       <c r="C71" s="6">
         <v>1</v>
       </c>
-      <c r="D71" s="8"/>
+      <c r="D71" s="8">
+        <v>38</v>
+      </c>
       <c r="E71" s="11" t="s">
         <v>24</v>
       </c>
@@ -2838,75 +2858,83 @@
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C72" s="6">
+        <v>1</v>
+      </c>
+      <c r="D72" s="8">
+        <v>38</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C72" s="6">
-        <v>1</v>
-      </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="11" t="s">
+      <c r="C73" s="6">
+        <v>1</v>
+      </c>
+      <c r="D73" s="8">
+        <v>38</v>
+      </c>
+      <c r="E73" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F73" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="14" t="s">
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C73" s="18">
-        <f>SUM(C62:C72)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="19" t="e">
-        <f>AVERAGE(D62:D72)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E73" s="33"/>
-      <c r="F73" s="34"/>
-    </row>
-    <row r="74" ht="18" customHeight="1"/>
+      <c r="C74" s="18">
+        <f>SUM(C62:C73)</f>
+      </c>
+      <c r="D74" s="19">
+        <f>IFERROR(SUMPRODUCT(C62:C73,D62:D73)/SUM(C62:C73),"")</f>
+      </c>
+      <c r="E74" s="33"/>
+      <c r="F74" s="34"/>
+    </row>
     <row r="75" ht="18" customHeight="1"/>
     <row r="76" ht="18" customHeight="1"/>
-    <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="45" t="s">
+    <row r="77" ht="18" customHeight="1"/>
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="D77" s="45"/>
-      <c r="E77" s="45"/>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="45"/>
       <c r="D78" s="45"/>
       <c r="E78" s="45"/>
     </row>
-    <row r="79" ht="18" customHeight="1"/>
-    <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="5" t="s">
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="45"/>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+    </row>
+    <row r="80" ht="18" customHeight="1"/>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D81" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E81" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F81" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" s="6"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="B82" s="2" t="s">
@@ -2919,7 +2947,7 @@
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C83" s="6"/>
       <c r="D83" s="8"/>
@@ -2935,9 +2963,9 @@
       <c r="E84" s="11"/>
       <c r="F84" s="11"/>
     </row>
-    <row r="85">
+    <row r="85" ht="18" customHeight="1">
       <c r="B85" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6"/>
       <c r="D85" s="8"/>
@@ -2955,7 +2983,7 @@
     </row>
     <row r="87">
       <c r="B87" s="2" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C87" s="6"/>
       <c r="D87" s="8"/>
@@ -2964,7 +2992,7 @@
     </row>
     <row r="88">
       <c r="B88" s="2" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="8"/>
@@ -2973,38 +3001,46 @@
     </row>
     <row r="89">
       <c r="B89" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C89" s="6"/>
       <c r="D89" s="8"/>
       <c r="E89" s="11"/>
       <c r="F89" s="11"/>
     </row>
-    <row r="90" ht="15.75">
+    <row r="90">
       <c r="B90" s="2" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="8"/>
       <c r="E90" s="11"/>
       <c r="F90" s="11"/>
     </row>
-    <row r="91" ht="19.5">
-      <c r="B91" s="14" t="s">
+    <row r="91" ht="15.75">
+      <c r="B91" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C91" s="6"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+    </row>
+    <row r="92" ht="19.5">
+      <c r="B92" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C91" s="18">
-        <f>SUM(C81:C90)</f>
+      <c r="C92" s="18">
+        <f>SUM(C82:C91)</f>
         <v>0</v>
       </c>
-      <c r="D91" s="19" t="e">
-        <f>AVERAGE(D81:D90)</f>
+      <c r="D92" s="19" t="e">
+        <f>AVERAGE(D82:D91)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E91" s="33"/>
-      <c r="F91" s="34"/>
-    </row>
-    <row r="93" ht="18" customHeight="1"/>
+      <c r="E92" s="33"/>
+      <c r="F92" s="34"/>
+    </row>
     <row r="94" ht="18" customHeight="1"/>
     <row r="95" ht="18" customHeight="1"/>
     <row r="96" ht="18" customHeight="1"/>
@@ -3017,12 +3053,13 @@
     <row r="103" ht="18" customHeight="1"/>
     <row r="104" ht="18" customHeight="1"/>
     <row r="105" ht="18" customHeight="1"/>
+    <row r="106" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C77:E77"/>
     <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C25:E25"/>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>Semana</t>
   </si>
@@ -495,7 +495,34 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve">Semana </t>
+    <t>Paraguay (USD/caja)</t>
+  </si>
+  <si>
+    <t>Paraguay MS</t>
+  </si>
+  <si>
+    <t>7 USD</t>
+  </si>
+  <si>
+    <t>lunes</t>
+  </si>
+  <si>
+    <t>Paraguay DF</t>
+  </si>
+  <si>
+    <t>martes</t>
+  </si>
+  <si>
+    <t>Paraguay AS</t>
+  </si>
+  <si>
+    <t>Semana 41</t>
+  </si>
+  <si>
+    <t>05/10 al 10/10</t>
+  </si>
+  <si>
+    <t>Celso</t>
   </si>
 </sst>
 </file>
@@ -2043,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="B2:J92"/>
+  <dimension ref="B2:J103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -2088,7 +2115,7 @@
         <v>18</v>
       </c>
       <c r="J5" s="12">
-        <f>SUM(C21,C36,C54,C74,C92)</f>
+        <f>SUM(C21,C36,C54,C74,C97)</f>
         <v>14.5</v>
       </c>
     </row>
@@ -2112,7 +2139,7 @@
         <v>21</v>
       </c>
       <c r="J6" s="12" t="e">
-        <f>AVERAGE(D21,D36,D54,D74,D92)</f>
+        <f>AVERAGE(D21,D36,D54,D74,D97)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2694,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>29</v>
@@ -2711,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>29</v>
@@ -2813,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>24</v>
@@ -2903,163 +2930,354 @@
       <c r="E74" s="33"/>
       <c r="F74" s="34"/>
     </row>
-    <row r="75" ht="18" customHeight="1"/>
-    <row r="76" ht="18" customHeight="1"/>
-    <row r="77" ht="18" customHeight="1"/>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="45" t="s">
+    <row r="75">
+      <c r="B75" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="D78" s="45"/>
-      <c r="E78" s="45"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="45"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" s="0">
+        <v>1</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" s="0">
+        <v>1</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="0">
+        <v>1</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C79" s="0">
+        <v>1</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="80" ht="18" customHeight="1"/>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="5" t="s">
+    <row r="81" ht="18" customHeight="1"/>
+    <row r="82" ht="18" customHeight="1"/>
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="D83" s="45"/>
+      <c r="E83" s="45"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="C84" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" s="45"/>
+      <c r="E84" s="45"/>
+    </row>
+    <row r="85" ht="18" customHeight="1"/>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D86" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E86" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F86" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="2" t="s">
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C82" s="6"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="2" t="s">
+      <c r="C87" s="6">
+        <v>1</v>
+      </c>
+      <c r="D87" s="8">
+        <v>35</v>
+      </c>
+      <c r="E87" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C83" s="6"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="6"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="6"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-    </row>
-    <row r="86">
-      <c r="B86" s="2" t="s">
+      <c r="C88" s="6">
+        <v>1</v>
+      </c>
+      <c r="D88" s="8">
+        <v>35</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="B89" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C86" s="6"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-    </row>
-    <row r="87">
-      <c r="B87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C88" s="6"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C89" s="6"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-    </row>
-    <row r="90">
+      <c r="C89" s="6">
+        <v>1</v>
+      </c>
+      <c r="D89" s="8">
+        <v>36</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
       <c r="B90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C90" s="6"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
-    </row>
-    <row r="91" ht="15.75">
+      <c r="C90" s="6">
+        <v>1</v>
+      </c>
+      <c r="D90" s="8">
+        <v>43</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="91">
       <c r="B91" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-    </row>
-    <row r="92" ht="19.5">
-      <c r="B92" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91" s="6">
+        <v>1</v>
+      </c>
+      <c r="D91" s="8">
+        <v>43</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" s="6">
+        <v>1</v>
+      </c>
+      <c r="D92" s="8">
+        <v>38</v>
+      </c>
+      <c r="E92" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="6">
+        <v>1</v>
+      </c>
+      <c r="D93" s="8">
+        <v>36</v>
+      </c>
+      <c r="E93" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C94" s="6">
+        <v>1</v>
+      </c>
+      <c r="D94" s="8">
+        <v>43</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="2"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
+    </row>
+    <row r="96" ht="15.75">
+      <c r="B96" s="2"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+    </row>
+    <row r="97" ht="19.5">
+      <c r="B97" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C92" s="18">
-        <f>SUM(C82:C91)</f>
-        <v>0</v>
-      </c>
-      <c r="D92" s="19" t="e">
-        <f>AVERAGE(D82:D91)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E92" s="33"/>
-      <c r="F92" s="34"/>
-    </row>
-    <row r="94" ht="18" customHeight="1"/>
-    <row r="95" ht="18" customHeight="1"/>
-    <row r="96" ht="18" customHeight="1"/>
-    <row r="97" ht="18" customHeight="1"/>
-    <row r="98" ht="18" customHeight="1"/>
-    <row r="99" ht="18" customHeight="1"/>
-    <row r="100" ht="18" customHeight="1"/>
-    <row r="101" ht="18" customHeight="1"/>
-    <row r="102" ht="18" customHeight="1"/>
-    <row r="103" ht="18" customHeight="1"/>
+      <c r="C97" s="18">
+        <f>SUM(C87:C96)</f>
+      </c>
+      <c r="D97" s="19">
+        <f>IFERROR(SUMPRODUCT(C87:C96,D87:D96)/SUM(C87:C96),"")</f>
+      </c>
+      <c r="E97" s="33"/>
+      <c r="F97" s="34"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C99" s="0">
+        <v>1</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C100" s="0">
+        <v>1</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="C101" s="0">
+        <v>1</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="C102" s="0">
+        <v>1</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C103" s="0">
+        <v>1</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
     <row r="104" ht="18" customHeight="1"/>
     <row r="105" ht="18" customHeight="1"/>
     <row r="106" ht="18" customHeight="1"/>
+    <row r="107" ht="18" customHeight="1"/>
+    <row r="108" ht="18" customHeight="1"/>
+    <row r="109" ht="18" customHeight="1"/>
+    <row r="110" ht="18" customHeight="1"/>
+    <row r="111" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C25:E25"/>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>Semana</t>
   </si>
@@ -523,6 +523,33 @@
   </si>
   <si>
     <t>Celso</t>
+  </si>
+  <si>
+    <t>Semana 42</t>
+  </si>
+  <si>
+    <t>12/10 al 17/10</t>
+  </si>
+  <si>
+    <t>miercoles</t>
+  </si>
+  <si>
+    <t>Semana 43</t>
+  </si>
+  <si>
+    <t>19/10 al 24/10</t>
+  </si>
+  <si>
+    <t>Muller Fabricio</t>
+  </si>
+  <si>
+    <t>Jaime Zimerman</t>
+  </si>
+  <si>
+    <t>Paraguay GM</t>
+  </si>
+  <si>
+    <t>7,5 USD</t>
   </si>
 </sst>
 </file>
@@ -2070,7 +2097,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="B2:J103"/>
+  <dimension ref="A2:J157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -3267,11 +3294,685 @@
     <row r="104" ht="18" customHeight="1"/>
     <row r="105" ht="18" customHeight="1"/>
     <row r="106" ht="18" customHeight="1"/>
-    <row r="107" ht="18" customHeight="1"/>
-    <row r="108" ht="18" customHeight="1"/>
+    <row r="107" ht="18" customHeight="1">
+      <c r="C107" s="0" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="0" t="s">
+        <v>148</v>
+      </c>
+    </row>
     <row r="109" ht="18" customHeight="1"/>
-    <row r="110" ht="18" customHeight="1"/>
-    <row r="111" ht="18" customHeight="1"/>
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="F110" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" s="0">
+        <v>1</v>
+      </c>
+      <c r="D111" s="0">
+        <v>35</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="0">
+        <v>1</v>
+      </c>
+      <c r="D112" s="0">
+        <v>35</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="0">
+        <v>1</v>
+      </c>
+      <c r="D113" s="0">
+        <v>35</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F113" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="0">
+        <v>1</v>
+      </c>
+      <c r="D114" s="0">
+        <v>35</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F114" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="0">
+        <v>1</v>
+      </c>
+      <c r="D115" s="0">
+        <v>35</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F115" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" s="0">
+        <v>1</v>
+      </c>
+      <c r="D116" s="0">
+        <v>35</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F116" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C117" s="0">
+        <v>1</v>
+      </c>
+      <c r="D117" s="0">
+        <v>38</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F117" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C118" s="0">
+        <v>1</v>
+      </c>
+      <c r="D118" s="0">
+        <v>38</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F118" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C119" s="0">
+        <v>1</v>
+      </c>
+      <c r="D119" s="0">
+        <v>40</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F119" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C120" s="0">
+        <v>1</v>
+      </c>
+      <c r="D120" s="0">
+        <v>38</v>
+      </c>
+      <c r="E120" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F120" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="C121" s="0">
+        <v>1</v>
+      </c>
+      <c r="D121" s="0">
+        <v>40</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F121" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" s="0">
+        <v>1</v>
+      </c>
+      <c r="D122" s="0">
+        <v>38</v>
+      </c>
+      <c r="E122" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F122" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="0">
+        <v>1</v>
+      </c>
+      <c r="D123" s="0">
+        <v>38</v>
+      </c>
+      <c r="E123" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F123" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C124" s="0">
+        <v>1</v>
+      </c>
+      <c r="D124" s="0">
+        <v>38</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F124" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C125" s="0">
+        <f>SUM(C111:C124)</f>
+      </c>
+      <c r="D125" s="0">
+        <f>IFERROR(SUMPRODUCT(C111:C124,D111:D124)/SUM(C111:C124),"")</f>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C127" s="0">
+        <v>1</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C128" s="0">
+        <v>1</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132">
+      <c r="C132" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="C133" s="0" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="134"/>
+    <row r="135">
+      <c r="B135" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="F135" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="0">
+        <v>1</v>
+      </c>
+      <c r="D136" s="0">
+        <v>35</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" s="0">
+        <v>1</v>
+      </c>
+      <c r="D137" s="0">
+        <v>35</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C138" s="0">
+        <v>1</v>
+      </c>
+      <c r="D138" s="0">
+        <v>38</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F138" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C139" s="0">
+        <v>1</v>
+      </c>
+      <c r="D139" s="0">
+        <v>38</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C140" s="0">
+        <v>1</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F140" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C141" s="0">
+        <v>1</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F141" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="0">
+        <v>1</v>
+      </c>
+      <c r="D142" s="0">
+        <v>35</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C143" s="0">
+        <v>1</v>
+      </c>
+      <c r="D143" s="0">
+        <v>35</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F143" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C144" s="0">
+        <v>1</v>
+      </c>
+      <c r="D144" s="0">
+        <v>35</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C145" s="0">
+        <v>1</v>
+      </c>
+      <c r="D145" s="0">
+        <v>38</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F145" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C146" s="0">
+        <v>1</v>
+      </c>
+      <c r="D146" s="0">
+        <v>40</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F146" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="C147" s="0">
+        <v>1</v>
+      </c>
+      <c r="D147" s="0">
+        <v>38</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="0">
+        <v>1</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="0">
+        <v>1</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="0">
+        <v>1</v>
+      </c>
+      <c r="D150" s="0">
+        <v>38</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C151" s="0">
+        <v>1</v>
+      </c>
+      <c r="D151" s="0">
+        <v>38</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F151" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C152" s="0">
+        <v>1</v>
+      </c>
+      <c r="D152" s="0">
+        <v>38</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F152" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C153" s="0">
+        <v>1</v>
+      </c>
+      <c r="D153" s="0">
+        <v>38</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F153" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" s="0">
+        <f>SUM(C136:C153)</f>
+      </c>
+      <c r="D154" s="0">
+        <f>IFERROR(SUMPRODUCT(C136:C153,D136:D153)/SUM(C136:C153),"")</f>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C156" s="0">
+        <v>1</v>
+      </c>
+      <c r="D156" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E156" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C157" s="0">
+        <v>1</v>
+      </c>
+      <c r="D157" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="E157" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="C58:E58"/>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>Semana</t>
   </si>
@@ -544,6 +544,12 @@
   </si>
   <si>
     <t>Jaime Zimerman</t>
+  </si>
+  <si>
+    <t>BAHIA</t>
+  </si>
+  <si>
+    <t>Sergio Correia</t>
   </si>
   <si>
     <t>Paraguay GM</t>
@@ -2097,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="A2:J157"/>
+  <dimension ref="B2:J159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -3604,9 +3610,6 @@
         <v>149</v>
       </c>
     </row>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
     <row r="132">
       <c r="C132" s="0" t="s">
         <v>150</v>
@@ -3617,7 +3620,6 @@
         <v>151</v>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="B135" s="0" t="s">
         <v>2</v>
@@ -3931,45 +3933,70 @@
     </row>
     <row r="154">
       <c r="B154" s="0" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="C154" s="0">
-        <f>SUM(C136:C153)</f>
+        <v>1</v>
       </c>
       <c r="D154" s="0">
-        <f>IFERROR(SUMPRODUCT(C136:C153,D136:D153)/SUM(C136:C153),"")</f>
+        <v>38</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="0" t="s">
-        <v>137</v>
+        <v>155</v>
+      </c>
+      <c r="C155" s="0">
+        <v>1</v>
+      </c>
+      <c r="D155" s="0">
+        <v>36</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="0" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="C156" s="0">
-        <v>1</v>
-      </c>
-      <c r="D156" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="E156" s="0" t="s">
-        <v>140</v>
+        <f>SUM(C136:C155)</f>
+      </c>
+      <c r="D156" s="0">
+        <f>IFERROR(SUMPRODUCT(C136:C155,D136:D155)/SUM(C136:C155),"")</f>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="C157" s="0">
-        <v>1</v>
-      </c>
-      <c r="D157" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="E157" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C158" s="0">
+        <v>1</v>
+      </c>
+      <c r="D158" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E158" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C159" s="0">
+        <v>1</v>
+      </c>
+      <c r="D159" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="E159" s="0" t="s">
         <v>140</v>
       </c>
     </row>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
   <si>
     <t>Semana</t>
   </si>
@@ -538,18 +538,6 @@
   </si>
   <si>
     <t>19/10 al 24/10</t>
-  </si>
-  <si>
-    <t>Muller Fabricio</t>
-  </si>
-  <si>
-    <t>Jaime Zimerman</t>
-  </si>
-  <si>
-    <t>BAHIA</t>
-  </si>
-  <si>
-    <t>Sergio Correia</t>
   </si>
   <si>
     <t>Paraguay GM</t>
@@ -2103,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="B2:J159"/>
+  <dimension ref="B2:J138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -3639,36 +3627,18 @@
     </row>
     <row r="136">
       <c r="B136" s="0" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C136" s="0">
-        <v>1</v>
+        <f>SUM(C136:C135)</f>
       </c>
       <c r="D136" s="0">
-        <v>35</v>
-      </c>
-      <c r="E136" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F136" s="0" t="s">
-        <v>23</v>
+        <f>IFERROR(SUMPRODUCT(C136:C135,D136:D135)/SUM(C136:C135),"")</f>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137" s="0">
-        <v>1</v>
-      </c>
-      <c r="D137" s="0">
-        <v>35</v>
-      </c>
-      <c r="E137" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F137" s="0" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
     </row>
     <row r="138">
@@ -3678,325 +3648,10 @@
       <c r="C138" s="0">
         <v>1</v>
       </c>
-      <c r="D138" s="0">
-        <v>38</v>
+      <c r="D138" s="0" t="s">
+        <v>153</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F138" s="0" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="C139" s="0">
-        <v>1</v>
-      </c>
-      <c r="D139" s="0">
-        <v>38</v>
-      </c>
-      <c r="E139" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F139" s="0" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C140" s="0">
-        <v>1</v>
-      </c>
-      <c r="E140" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F140" s="0" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C141" s="0">
-        <v>1</v>
-      </c>
-      <c r="E141" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F141" s="0" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C142" s="0">
-        <v>1</v>
-      </c>
-      <c r="D142" s="0">
-        <v>35</v>
-      </c>
-      <c r="E142" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F142" s="0" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C143" s="0">
-        <v>1</v>
-      </c>
-      <c r="D143" s="0">
-        <v>35</v>
-      </c>
-      <c r="E143" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F143" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C144" s="0">
-        <v>1</v>
-      </c>
-      <c r="D144" s="0">
-        <v>35</v>
-      </c>
-      <c r="E144" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F144" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="C145" s="0">
-        <v>1</v>
-      </c>
-      <c r="D145" s="0">
-        <v>38</v>
-      </c>
-      <c r="E145" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F145" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C146" s="0">
-        <v>1</v>
-      </c>
-      <c r="D146" s="0">
-        <v>40</v>
-      </c>
-      <c r="E146" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F146" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="C147" s="0">
-        <v>1</v>
-      </c>
-      <c r="D147" s="0">
-        <v>38</v>
-      </c>
-      <c r="E147" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="F147" s="0" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="0">
-        <v>1</v>
-      </c>
-      <c r="E148" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F148" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149" s="0">
-        <v>1</v>
-      </c>
-      <c r="E149" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F149" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C150" s="0">
-        <v>1</v>
-      </c>
-      <c r="D150" s="0">
-        <v>38</v>
-      </c>
-      <c r="E150" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F150" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C151" s="0">
-        <v>1</v>
-      </c>
-      <c r="D151" s="0">
-        <v>38</v>
-      </c>
-      <c r="E151" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F151" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="C152" s="0">
-        <v>1</v>
-      </c>
-      <c r="D152" s="0">
-        <v>38</v>
-      </c>
-      <c r="E152" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F152" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="B153" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="C153" s="0">
-        <v>1</v>
-      </c>
-      <c r="D153" s="0">
-        <v>38</v>
-      </c>
-      <c r="E153" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F153" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="C154" s="0">
-        <v>1</v>
-      </c>
-      <c r="D154" s="0">
-        <v>38</v>
-      </c>
-      <c r="E154" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C155" s="0">
-        <v>1</v>
-      </c>
-      <c r="D155" s="0">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C156" s="0">
-        <f>SUM(C136:C155)</f>
-      </c>
-      <c r="D156" s="0">
-        <f>IFERROR(SUMPRODUCT(C136:C155,D136:D155)/SUM(C136:C155),"")</f>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="0" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="C158" s="0">
-        <v>1</v>
-      </c>
-      <c r="D158" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="E158" s="0" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C159" s="0">
-        <v>1</v>
-      </c>
-      <c r="D159" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="E159" s="0" t="s">
         <v>140</v>
       </c>
     </row>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>Semana</t>
   </si>
@@ -538,6 +538,18 @@
   </si>
   <si>
     <t>19/10 al 24/10</t>
+  </si>
+  <si>
+    <t>Muller Fabricio</t>
+  </si>
+  <si>
+    <t>BAHIA</t>
+  </si>
+  <si>
+    <t>Jhony Viera</t>
+  </si>
+  <si>
+    <t>Jaime Zimerman</t>
   </si>
   <si>
     <t>Paraguay GM</t>
@@ -2091,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="B2:J138"/>
+  <dimension ref="B2:J161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -3627,18 +3639,36 @@
     </row>
     <row r="136">
       <c r="B136" s="0" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C136" s="0">
-        <f>SUM(C136:C135)</f>
+        <v>1</v>
       </c>
       <c r="D136" s="0">
-        <f>IFERROR(SUMPRODUCT(C136:C135,D136:D135)/SUM(C136:C135),"")</f>
+        <v>35</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="0" t="s">
-        <v>137</v>
+        <v>9</v>
+      </c>
+      <c r="C137" s="0">
+        <v>1</v>
+      </c>
+      <c r="D137" s="0">
+        <v>35</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="138">
@@ -3648,10 +3678,383 @@
       <c r="C138" s="0">
         <v>1</v>
       </c>
-      <c r="D138" s="0" t="s">
+      <c r="D138" s="0">
+        <v>38</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F138" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C139" s="0">
+        <v>1</v>
+      </c>
+      <c r="D139" s="0">
+        <v>38</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C140" s="0">
+        <v>1</v>
+      </c>
+      <c r="D140" s="0">
+        <v>38</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F140" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C141" s="0">
+        <v>1</v>
+      </c>
+      <c r="D141" s="0">
+        <v>38</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F141" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C142" s="0">
+        <v>1</v>
+      </c>
+      <c r="D142" s="0">
+        <v>38</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C143" s="0">
+        <v>1</v>
+      </c>
+      <c r="D143" s="0">
+        <v>38</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F143" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="E138" s="0" t="s">
+      <c r="C144" s="0">
+        <v>1</v>
+      </c>
+      <c r="D144" s="0">
+        <v>38</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="0">
+        <v>1</v>
+      </c>
+      <c r="D145" s="0">
+        <v>36</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F145" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" s="0">
+        <v>1</v>
+      </c>
+      <c r="D146" s="0">
+        <v>35</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F146" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C147" s="0">
+        <v>1</v>
+      </c>
+      <c r="D147" s="0">
+        <v>35</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C148" s="0">
+        <v>1</v>
+      </c>
+      <c r="D148" s="0">
+        <v>35</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C149" s="0">
+        <v>1</v>
+      </c>
+      <c r="D149" s="0">
+        <v>38</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C150" s="0">
+        <v>1</v>
+      </c>
+      <c r="D150" s="0">
+        <v>38</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C151" s="0">
+        <v>1</v>
+      </c>
+      <c r="D151" s="0">
+        <v>38</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F151" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="C152" s="0">
+        <v>1</v>
+      </c>
+      <c r="D152" s="0">
+        <v>38</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F152" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="0">
+        <v>1</v>
+      </c>
+      <c r="D153" s="0">
+        <v>35</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F153" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="0">
+        <v>1</v>
+      </c>
+      <c r="D154" s="0">
+        <v>35</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F154" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" s="0">
+        <v>1</v>
+      </c>
+      <c r="D155" s="0">
+        <v>38</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F155" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C156" s="0">
+        <v>1</v>
+      </c>
+      <c r="D156" s="0">
+        <v>38</v>
+      </c>
+      <c r="E156" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F156" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C157" s="0">
+        <v>1</v>
+      </c>
+      <c r="D157" s="0">
+        <v>38</v>
+      </c>
+      <c r="E157" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F157" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C158" s="0">
+        <v>1</v>
+      </c>
+      <c r="D158" s="0">
+        <v>38</v>
+      </c>
+      <c r="E158" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F158" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="0">
+        <f>SUM(C136:C158)</f>
+      </c>
+      <c r="D159" s="0">
+        <f>IFERROR(SUMPRODUCT(C136:C158,D136:D158)/SUM(C136:C158),"")</f>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C161" s="0">
+        <v>1</v>
+      </c>
+      <c r="D161" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="E161" s="0" t="s">
         <v>140</v>
       </c>
     </row>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>Semana</t>
   </si>
@@ -556,6 +556,18 @@
   </si>
   <si>
     <t>7,5 USD</t>
+  </si>
+  <si>
+    <t>Semana 44</t>
+  </si>
+  <si>
+    <t>26/10 al 31/10</t>
+  </si>
+  <si>
+    <t>Andre Pauli</t>
+  </si>
+  <si>
+    <t>Aryste Mittelman</t>
   </si>
 </sst>
 </file>
@@ -2103,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="B2:J161"/>
+  <dimension ref="B2:J185"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -4056,6 +4068,268 @@
       </c>
       <c r="E161" s="0" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="C165" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="C166" s="0" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C168" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E168" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="F168" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C169" s="0">
+        <v>1</v>
+      </c>
+      <c r="D169" s="0">
+        <v>31</v>
+      </c>
+      <c r="E169" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" s="0">
+        <v>1</v>
+      </c>
+      <c r="D170" s="0">
+        <v>31</v>
+      </c>
+      <c r="E170" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C171" s="0">
+        <v>1</v>
+      </c>
+      <c r="D171" s="0">
+        <v>31</v>
+      </c>
+      <c r="E171" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" s="0">
+        <v>1</v>
+      </c>
+      <c r="D172" s="0">
+        <v>31</v>
+      </c>
+      <c r="E172" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C173" s="0">
+        <v>1</v>
+      </c>
+      <c r="D173" s="0">
+        <v>33</v>
+      </c>
+      <c r="E173" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="0">
+        <v>1</v>
+      </c>
+      <c r="D174" s="0">
+        <v>32</v>
+      </c>
+      <c r="E174" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="C175" s="0">
+        <v>1</v>
+      </c>
+      <c r="D175" s="0">
+        <v>33</v>
+      </c>
+      <c r="E175" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C176" s="0">
+        <v>1</v>
+      </c>
+      <c r="D176" s="0">
+        <v>33</v>
+      </c>
+      <c r="E176" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="C177" s="0">
+        <v>1</v>
+      </c>
+      <c r="D177" s="0">
+        <v>38</v>
+      </c>
+      <c r="E177" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C178" s="0">
+        <v>1</v>
+      </c>
+      <c r="D178" s="0">
+        <v>33</v>
+      </c>
+      <c r="E178" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C179" s="0">
+        <v>1</v>
+      </c>
+      <c r="D179" s="0">
+        <v>33</v>
+      </c>
+      <c r="E179" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C180" s="0">
+        <v>1</v>
+      </c>
+      <c r="D180" s="0">
+        <v>34</v>
+      </c>
+      <c r="E180" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C181" s="0">
+        <v>1</v>
+      </c>
+      <c r="D181" s="0">
+        <v>33</v>
+      </c>
+      <c r="E181" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C182" s="0">
+        <v>1</v>
+      </c>
+      <c r="D182" s="0">
+        <v>33</v>
+      </c>
+      <c r="E182" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C183" s="0">
+        <v>1</v>
+      </c>
+      <c r="D183" s="0">
+        <v>33</v>
+      </c>
+      <c r="E183" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="C184" s="0">
+        <v>1</v>
+      </c>
+      <c r="D184" s="0">
+        <v>33</v>
+      </c>
+      <c r="E184" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C185" s="0">
+        <f>SUM(C169:C184)</f>
+      </c>
+      <c r="D185" s="0">
+        <f>IFERROR(SUMPRODUCT(C169:C184,D169:D184)/SUM(C169:C184),"")</f>
       </c>
     </row>
   </sheetData>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>Semana</t>
   </si>
@@ -568,6 +568,9 @@
   </si>
   <si>
     <t>Aryste Mittelman</t>
+  </si>
+  <si>
+    <t>8 USD</t>
   </si>
 </sst>
 </file>
@@ -2115,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1258FB-3560-4958-9517-8E4782DDD67C}">
-  <dimension ref="B2:J185"/>
+  <dimension ref="B2:J189"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -4323,13 +4326,57 @@
     </row>
     <row r="185">
       <c r="B185" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C185" s="0">
+        <v>1</v>
+      </c>
+      <c r="D185" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C185" s="0">
-        <f>SUM(C169:C184)</f>
-      </c>
-      <c r="D185" s="0">
-        <f>IFERROR(SUMPRODUCT(C169:C184,D169:D184)/SUM(C169:C184),"")</f>
+      <c r="C186" s="0">
+        <f>SUM(C169:C185)</f>
+      </c>
+      <c r="D186" s="0">
+        <f>IFERROR(SUMPRODUCT(C169:C185,D169:D185)/SUM(C169:C185),"")</f>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C188" s="0">
+        <v>1</v>
+      </c>
+      <c r="D188" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="E188" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C189" s="0">
+        <v>1</v>
+      </c>
+      <c r="D189" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="E189" s="0" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -5847,7 +5894,7 @@
       </c>
       <c r="I6" s="12">
         <f>AVERAGE(D20,D41,D61,D82)</f>
-        <v>36.17628205128206</v>
+        <v>36.176282051282058</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -6959,7 +7006,7 @@
       </c>
       <c r="J6" s="12">
         <f>AVERAGE(D45,D22,D72,D99)</f>
-        <v>52.87730263157895</v>
+        <v>52.877302631578949</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -7903,7 +7950,7 @@
       </c>
       <c r="D72" s="19">
         <f>AVERAGE(D53:D71)</f>
-        <v>58.36842105263158</v>
+        <v>58.368421052631582</v>
       </c>
       <c r="E72" s="35">
         <v>1.92</v>
@@ -8276,7 +8323,7 @@
       </c>
       <c r="D99" s="19">
         <f>AVERAGE(D80:D98)</f>
-        <v>53.31578947368421</v>
+        <v>53.315789473684212</v>
       </c>
       <c r="E99" s="35">
         <v>1.89</v>
@@ -11017,7 +11064,7 @@
       </c>
       <c r="D19" s="19">
         <f>AVERAGE(D6:D18)</f>
-        <v>34.76923076923077</v>
+        <v>34.769230769230766</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="34"/>
@@ -11278,7 +11325,7 @@
       </c>
       <c r="D40" s="19">
         <f>AVERAGE(D27:D39)</f>
-        <v>37.69230769230769</v>
+        <v>37.692307692307693</v>
       </c>
       <c r="E40" s="33"/>
       <c r="F40" s="34"/>
@@ -11545,7 +11592,7 @@
       </c>
       <c r="D61" s="19">
         <f>AVERAGE(D48:D60)</f>
-        <v>42.61538461538461</v>
+        <v>42.615384615384613</v>
       </c>
       <c r="E61" s="35"/>
       <c r="F61" s="36"/>
@@ -12480,7 +12527,7 @@
       </c>
       <c r="D51" s="19">
         <f>AVERAGE(D40:D50)</f>
-        <v>42.54545454545455</v>
+        <v>42.545454545454547</v>
       </c>
       <c r="E51" s="33"/>
       <c r="F51" s="34"/>
@@ -12924,7 +12971,7 @@
       </c>
       <c r="J6" s="12">
         <f>AVERAGE(D14,D29,D47,D66,D84)</f>
-        <v>40.88298701298701</v>
+        <v>40.882987012987009</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -13222,7 +13269,7 @@
       </c>
       <c r="D29" s="19">
         <f>AVERAGE(D22:D28)</f>
-        <v>44.42857142857143</v>
+        <v>44.428571428571431</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="34"/>
@@ -13679,7 +13726,7 @@
       </c>
       <c r="D66" s="19">
         <f>AVERAGE(D55:D65)</f>
-        <v>37.63636363636363</v>
+        <v>37.636363636363633</v>
       </c>
       <c r="E66" s="33"/>
       <c r="F66" s="34"/>

--- a/fuentes/cargas 2026.xlsx
+++ b/fuentes/cargas 2026.xlsx
@@ -4334,6 +4334,9 @@
       <c r="D185" s="0">
         <v>31</v>
       </c>
+      <c r="E185" s="0" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="186">
       <c r="B186" s="0" t="s">
